--- a/public/modelSample.xlsx
+++ b/public/modelSample.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -435,9 +435,12 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,6 +529,21 @@
           <t>avgCharsPerToken</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>badges</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -564,10 +582,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -589,6 +603,21 @@
       <c r="Q2" t="n">
         <v>4</v>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ارزان و سریع — پیش‌فرض خوب برای اکثر کارهای روزمره</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>محبوب</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>LIARA,OPENROUTER</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,10 +656,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -652,6 +677,21 @@
       <c r="Q3" t="n">
         <v>4</v>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>قوی‌تر از mini، برای کارهای پیچیده‌تر</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ترند</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>LIARA,OPENROUTER</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -690,10 +730,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -715,6 +751,16 @@
       <c r="Q4" t="n">
         <v>4</v>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>بهترین انتخاب برای کدنویسی و تحلیل متن طولانی</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>LIARA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -790,6 +836,16 @@
       <c r="Q5" t="n">
         <v>4</v>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>تولید/ویرایش عکس با کیفیت بالا</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>LIARA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -828,10 +884,6 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -852,6 +904,11 @@
       </c>
       <c r="Q6" t="n">
         <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>LIARA</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -865,13 +922,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -904,7 +961,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>شناسه یکتای مدل (کلید اصلی برای افزودن/به‌روزرسانی) — دقیقاً همان id که برای صدازدن API لیارا استفاده می‌شود</t>
+          <t>شناسه یکتای مدل (کلید اصلی برای افزودن/به‌روزرسانی) — دقیقاً همان id که برای صدازدن API آن پلتفرم استفاده می‌شود</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -948,7 +1005,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>نام ارائه‌دهنده مدل</t>
+          <t>نام ارائه‌دهنده مدل (وندور — نه پلتفرم inference)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1271,7 +1328,73 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
+        <is>
+          <t>یک جمله‌ی کوتاه درباره‌ی کاربرد مدل — در صفحه‌ی انتخاب مدل کاربر نهایی نشان داده می‌شود</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ارزان و سریع — پیش‌فرض خوب برای اکثر کارها</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>badges</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>برچسب‌های فیلتر (ترند/محبوب/...) — با کاما جدا کنید، هر رشته دقیقاً همانی است که در صفحه‌ی انتخاب مدل نمایش داده می‌شود</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>خیر</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ترند,محبوب</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>این name دقیقاً روی کدام پلتفرم(های) inference معتبر است — لیارا و OpenRouter برای یک «مدل منطقی» یکسان همیشه یک شناسه‌ی یکسان ندارند؛ اگر مطمئن نیستید فقط همان پلتفرمی که همین الان استفاده می‌کنید را بگذارید. با کاما جدا کنید</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>بله</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LIARA,OPENROUTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>نکته: اگر name یک مدل موجود در سیستم باشد، اطلاعات آن به‌روزرسانی می‌شود؛ در غیر این صورت مدل جدید ساخته می‌شود.</t>
         </is>
